--- a/src/main/resources/be/vlaanderen/bodemenondergrond/data/id/conceptscheme/bemonsteringsprocedure/bemonsteringsprocedure.xlsx
+++ b/src/main/resources/be/vlaanderen/bodemenondergrond/data/id/conceptscheme/bemonsteringsprocedure/bemonsteringsprocedure.xlsx
@@ -483,7 +483,7 @@
         <v>https://app.nbn.be/data/r/platform/frontend/detail?p40_id=188163&amp;p40_language_code=en&amp;p40_detail_id=98267</v>
       </c>
       <c r="E3" t="str">
-        <v>NBN EN ISO standaard voor 'Geotechnical investigation and testing - Sampling methods and groundwater measurements - Part 1: Technical principles for the sampling of soil, rock and groundwater' versie 2021.</v>
+        <v>NBN EN ISO standaard voor 'Geotechnical investigation and testing - Sampling methods and groundwater measurements - Part 1: Technical principles for the sampling of soil, rock and groundwater' versie 2021.</v>
       </c>
       <c r="F3" t="str">
         <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/bemonsteringsprocedure</v>
@@ -492,7 +492,7 @@
         <v>22475-1-2021</v>
       </c>
       <c r="H3" t="str">
-        <v>NBN EN ISO standaard voor 'Geotechnical investigation and testing - Sampling methods and groundwater measurements - Part 1: Technical principles for the sampling of soil, rock and groundwater' versie 2021.</v>
+        <v>NBN EN ISO standaard voor 'Geotechnical investigation and testing - Sampling methods and groundwater measurements - Part 1: Technical principles for the sampling of soil, rock and groundwater' versie 2021.</v>
       </c>
       <c r="I3" t="str">
         <v>NBN EN ISO 22475-1:2021</v>
@@ -763,7 +763,7 @@
         <v>https://omgeving.vlaanderen.be/sites/default/files/2023-05/protocol%20staalname%20Cmon%201.1%20-%20werkdocument.pdf</v>
       </c>
       <c r="E11" t="str">
-        <v>Het staalnameprotocol voor de bodembemonstering aan de hand van een grondboring voor het bepalen van de koolstofvoorraad binnen het Vlaamse bodemkoolstofmonitoringnetwerk 'Cmon'.</v>
+        <v>Het staalnameprotocol voor de bodembemonstering aan de hand van een grondboring voor het bepalen van de koolstofvoorraad binnen het Vlaamse bodemkoolstofmonitoringnetwerk 'Cmon'.</v>
       </c>
       <c r="F11" t="str">
         <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/bemonsteringsprocedure</v>
@@ -772,7 +772,7 @@
         <v>csp</v>
       </c>
       <c r="H11" t="str">
-        <v>Het staalnameprotocol voor de bodembemonstering aan de hand van een grondboring voor het bepalen van de koolstofvoorraad binnen het Vlaamse bodemkoolstofmonitoringnetwerk 'Cmon'.</v>
+        <v>Het staalnameprotocol voor de bodembemonstering aan de hand van een grondboring voor het bepalen van de koolstofvoorraad binnen het Vlaamse bodemkoolstofmonitoringnetwerk 'Cmon'.</v>
       </c>
       <c r="I11" t="str">
         <v>Cmon staalnameprotocol</v>
@@ -798,7 +798,7 @@
         <v>https://emis.vito.be/nl/erkende-laboratoria/water-gop/compendium-wac</v>
       </c>
       <c r="E12" t="str">
-        <v>Het compendium voor de monsterneming, meting en analyse van water voor  laboratoria in het kader van de Vlaamse erkenningswetgeving VLAREL.</v>
+        <v>Het compendium voor de monsterneming, meting en analyse van water voor laboratoria in het kader van de Vlaamse erkenningswetgeving VLAREL.</v>
       </c>
       <c r="F12" t="str">
         <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/bemonsteringsprocedure</v>
@@ -807,7 +807,7 @@
         <v>wac</v>
       </c>
       <c r="H12" t="str">
-        <v>Het compendium voor de monsterneming, meting en analyse van water voor  laboratoria in het kader van de Vlaamse erkenningswetgeving VLAREL.</v>
+        <v>Het compendium voor de monsterneming, meting en analyse van water voor laboratoria in het kader van de Vlaamse erkenningswetgeving VLAREL.</v>
       </c>
       <c r="I12" t="str">
         <v>Compendium WAC</v>
